--- a/results/L2_causal_discovery/L2_Cuproptosis_Causal_DAG.xlsx
+++ b/results/L2_causal_discovery/L2_Cuproptosis_Causal_DAG.xlsx
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K2" t="n">
         <v>12</v>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
         <v>6</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
         <v>14</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2094,19 +2094,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[PASS]</t>
+          <t>[FAIL]</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>6</v>
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>≥ 0.2</t>
+          <t>&gt;= 0.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[PASS]</t>
+          <t>[FAIL]</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2669,17 +2669,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SCO1</t>
+          <t>SLC31A1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COX17</t>
+          <t>FDX1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2691,12 +2691,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SLC31A1</t>
+          <t>STEAP3</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FDX1</t>
+          <t>SLC11A2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2705,28 +2705,6 @@
         </is>
       </c>
       <c r="D22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STEAP3</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SLC11A2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
